--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -363,42 +363,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sum_visits</t>
+          <t>mean_visit_per_year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_count</t>
+          <t>min_visit_per_year</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>min_visits</t>
+          <t>max_visit_per_year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>max_visits</t>
+          <t>sd_visit_per_year</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sd_visits</t>
+          <t>median_visit_per_year</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median_visits</t>
+          <t>lower_q_visits_per_year</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q1_visits</t>
+          <t>upper_q_visits_per_year</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>q3_visits</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -407,28 +422,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>371820</v>
+        <v>14.52</v>
       </c>
       <c r="C2">
-        <v>16.01</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="E2">
-        <v>315</v>
+        <v>14.72</v>
       </c>
       <c r="F2">
-        <v>15.02</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>21</v>
+        <v>16978</v>
+      </c>
+      <c r="J2">
+        <v>0.11</v>
+      </c>
+      <c r="K2">
+        <v>14.3</v>
+      </c>
+      <c r="L2">
+        <v>14.75</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>195184</v>
+        <v>7.79</v>
       </c>
       <c r="C3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="D3">
+        <v>166</v>
+      </c>
+      <c r="E3">
+        <v>12.51</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>166</v>
-      </c>
-      <c r="F3">
-        <v>12.74</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
       <c r="H3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>16978</v>
+      </c>
+      <c r="J3">
+        <v>0.1</v>
+      </c>
+      <c r="K3">
+        <v>7.6</v>
+      </c>
+      <c r="L3">
+        <v>7.98</v>
       </c>
     </row>
   </sheetData>
@@ -467,7 +500,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -478,42 +511,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sum_visits</t>
+          <t>mean_visit_per_year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_count</t>
+          <t>min_visit_per_year</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>min_visits</t>
+          <t>max_visit_per_year</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>max_visits</t>
+          <t>sd_visit_per_year</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sd_visits</t>
+          <t>median_visit_per_year</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median_visits</t>
+          <t>lower_q_visits_per_year</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q1_visits</t>
+          <t>upper_q_visits_per_year</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>q3_visits</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -522,28 +570,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>371820</v>
+        <v>13.93</v>
       </c>
       <c r="C2">
-        <v>15.52</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="E2">
-        <v>315</v>
+        <v>14.7</v>
       </c>
       <c r="F2">
-        <v>15.05</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I2">
-        <v>21</v>
+        <v>17705</v>
+      </c>
+      <c r="J2">
+        <v>0.11</v>
+      </c>
+      <c r="K2">
+        <v>13.71</v>
+      </c>
+      <c r="L2">
+        <v>14.15</v>
       </c>
     </row>
     <row r="3">
@@ -551,28 +608,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>195184</v>
+        <v>7.47</v>
       </c>
       <c r="C3">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="D3">
+        <v>166</v>
+      </c>
+      <c r="E3">
+        <v>12.35</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>166</v>
-      </c>
-      <c r="F3">
-        <v>12.63</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
       <c r="H3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>17705</v>
+      </c>
+      <c r="J3">
+        <v>0.09</v>
+      </c>
+      <c r="K3">
+        <v>7.29</v>
+      </c>
+      <c r="L3">
+        <v>7.65</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14.52</v>
+        <v>15.84</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>14.72</v>
+        <v>14.89</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>14.3</v>
+        <v>15.65</v>
       </c>
       <c r="L2">
-        <v>14.75</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.79</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -469,28 +469,28 @@
         <v>166</v>
       </c>
       <c r="E3">
-        <v>12.51</v>
+        <v>12.69</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="K3">
-        <v>7.6</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L3">
-        <v>7.98</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13.93</v>
+        <v>15.41</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>315</v>
       </c>
       <c r="E2">
-        <v>14.7</v>
+        <v>14.91</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>17705</v>
+        <v>22900</v>
       </c>
       <c r="J2">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>13.71</v>
+        <v>15.22</v>
       </c>
       <c r="L2">
-        <v>14.15</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="3">
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.47</v>
+        <v>8.07</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -617,28 +617,28 @@
         <v>166</v>
       </c>
       <c r="E3">
-        <v>12.35</v>
+        <v>12.58</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <v>17705</v>
+        <v>22900</v>
       </c>
       <c r="J3">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="K3">
-        <v>7.29</v>
+        <v>7.91</v>
       </c>
       <c r="L3">
-        <v>7.65</v>
+        <v>8.23</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
@@ -1,22 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_01EC0D128C9153A658C55120E38FB759BFF15288" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unadjusted_user_summary" sheetId="1" r:id="rId1"/>
     <sheet name="unadjusted_all_summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+  <si>
+    <t>year_after_index</t>
+  </si>
+  <si>
+    <t>mean_visit_per_year</t>
+  </si>
+  <si>
+    <t>min_visit_per_year</t>
+  </si>
+  <si>
+    <t>max_visit_per_year</t>
+  </si>
+  <si>
+    <t>sd_visit_per_year</t>
+  </si>
+  <si>
+    <t>median_visit_per_year</t>
+  </si>
+  <si>
+    <t>lower_q_visits_per_year</t>
+  </si>
+  <si>
+    <t>upper_q_visits_per_year</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +111,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +232,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,73 +408,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year_after_index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mean_visit_per_year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>min_visit_per_year</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>max_visit_per_year</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sd_visit_per_year</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>median_visit_per_year</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lower_q_visits_per_year</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>upper_q_visits_per_year</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>lower</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>upper</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -455,12 +488,12 @@
         <v>16.04</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.289999999999999</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -487,10 +520,10 @@
         <v>0.08</v>
       </c>
       <c r="K3">
-        <v>8.130000000000001</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="L3">
-        <v>8.460000000000001</v>
+        <v>8.4600000000000009</v>
       </c>
     </row>
   </sheetData>
@@ -499,73 +532,49 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year_after_index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mean_visit_per_year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>min_visit_per_year</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>max_visit_per_year</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>sd_visit_per_year</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>median_visit_per_year</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>lower_q_visits_per_year</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>upper_q_visits_per_year</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>lower</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>upper</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -603,7 +612,7 @@
         <v>15.61</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted.xlsx
@@ -1,69 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_01EC0D128C9153A658C55120E38FB759BFF15288" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="unadjusted_user_summary" sheetId="1" r:id="rId1"/>
     <sheet name="unadjusted_all_summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
-  <si>
-    <t>year_after_index</t>
-  </si>
-  <si>
-    <t>mean_visit_per_year</t>
-  </si>
-  <si>
-    <t>min_visit_per_year</t>
-  </si>
-  <si>
-    <t>max_visit_per_year</t>
-  </si>
-  <si>
-    <t>sd_visit_per_year</t>
-  </si>
-  <si>
-    <t>median_visit_per_year</t>
-  </si>
-  <si>
-    <t>lower_q_visits_per_year</t>
-  </si>
-  <si>
-    <t>upper_q_visits_per_year</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>se</t>
-  </si>
-  <si>
-    <t>lower</t>
-  </si>
-  <si>
-    <t>upper</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -197,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -232,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -408,122 +351,146 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year_after_index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visit_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>min_visit_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.84</v>
+        <v>60.3</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>315</v>
+        <v>1099</v>
       </c>
       <c r="E2">
-        <v>14.89</v>
+        <v>62.93</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="I2">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="K2">
-        <v>15.65</v>
+        <v>59.47</v>
       </c>
       <c r="L2">
-        <v>16.04</v>
+        <v>61.12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.2899999999999991</v>
+        <v>33.18</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>166</v>
+        <v>821</v>
       </c>
       <c r="E3">
-        <v>12.69</v>
+        <v>53.89</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I3">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="J3">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="K3">
-        <v>8.1300000000000008</v>
+        <v>32.47</v>
       </c>
       <c r="L3">
-        <v>8.4600000000000009</v>
+        <v>33.89</v>
       </c>
     </row>
   </sheetData>
@@ -532,122 +499,146 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year_after_index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visit_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>min_visit_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.41</v>
+        <v>112.79</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>315</v>
+        <v>3592</v>
       </c>
       <c r="E2">
-        <v>14.91</v>
+        <v>110.04</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>146.25</v>
       </c>
       <c r="I2">
         <v>22900</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0.73</v>
       </c>
       <c r="K2">
-        <v>15.22</v>
+        <v>111.37</v>
       </c>
       <c r="L2">
-        <v>15.61</v>
+        <v>114.22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.07</v>
+        <v>53.88</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>166</v>
+        <v>2846</v>
       </c>
       <c r="E3">
-        <v>12.58</v>
+        <v>87.75</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="I3">
         <v>22900</v>
       </c>
       <c r="J3">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="K3">
-        <v>7.91</v>
+        <v>52.74</v>
       </c>
       <c r="L3">
-        <v>8.23</v>
+        <v>55.02</v>
       </c>
     </row>
   </sheetData>
